--- a/PERSONAL/PaySlips/1.Income Tax eFiling/AY 2026-27/Ragu Sir/STI-Vasanth-V1.xlsx
+++ b/PERSONAL/PaySlips/1.Income Tax eFiling/AY 2026-27/Ragu Sir/STI-Vasanth-V1.xlsx
@@ -1,25 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Income Tax Returns\IT Return 2025-26\Vasanth\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://elgi-my.sharepoint.com/personal/vasanthk_elgi_com/Documents/Desktop/Desktop Files/Vasanth_GitDesktop/Flatris-LAB/Flatris-LAB/VasanthRepos2/PERSONAL/PaySlips/1.Income Tax eFiling/AY 2026-27/Ragu Sir/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2228C4DE-4185-4970-94A4-CFAB24A4C6C9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{2228C4DE-4185-4970-94A4-CFAB24A4C6C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{396964B4-2DFC-488D-8E9D-CA9ADF007734}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="9765" xr2:uid="{532392AB-2ADB-409C-A92B-A4F5F23FB7B3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{532392AB-2ADB-409C-A92B-A4F5F23FB7B3}"/>
   </bookViews>
   <sheets>
     <sheet name="Computation" sheetId="1" r:id="rId1"/>
     <sheet name="Schedules(Landscape)" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Computation!$A$1:$G$93</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -709,7 +723,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -732,143 +746,146 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -888,9 +905,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -928,7 +945,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1034,7 +1051,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1176,7 +1193,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1197,99 +1214,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:92" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
       <c r="P1"/>
       <c r="CM1" s="6"/>
       <c r="CN1" s="6"/>
     </row>
     <row r="2" spans="1:92" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="41" t="s">
         <v>96</v>
       </c>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
       <c r="P2"/>
     </row>
     <row r="3" spans="1:92" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="41" t="s">
         <v>97</v>
       </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
     </row>
     <row r="4" spans="1:92" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
     </row>
     <row r="5" spans="1:92" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="41" t="s">
         <v>99</v>
       </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
     </row>
     <row r="6" spans="1:92" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
     </row>
     <row r="7" spans="1:92" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
     </row>
     <row r="8" spans="1:92" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
     </row>
     <row r="9" spans="1:92" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="10"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="40"/>
     </row>
     <row r="10" spans="1:92" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D10" s="28"/>
+      <c r="D10" s="20"/>
       <c r="E10" s="5" t="s">
         <v>7</v>
       </c>
@@ -1301,15 +1318,15 @@
       </c>
     </row>
     <row r="11" spans="1:92" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="29" t="s">
+      <c r="B11" s="21" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:92" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="22" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="7"/>
@@ -1324,7 +1341,7 @@
       <c r="D13" s="3">
         <v>2</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="12">
         <v>1940667</v>
       </c>
     </row>
@@ -1332,7 +1349,7 @@
       <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="17">
         <v>75000</v>
       </c>
     </row>
@@ -1340,7 +1357,7 @@
       <c r="B15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="12">
         <v>1865667</v>
       </c>
     </row>
@@ -1348,15 +1365,15 @@
       <c r="B16" s="3"/>
     </row>
     <row r="17" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="29" t="s">
+      <c r="B17" s="21" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="30" t="s">
+      <c r="B18" s="22" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1364,7 +1381,7 @@
       <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F19" s="20">
+      <c r="F19" s="12">
         <v>-5544</v>
       </c>
     </row>
@@ -1372,16 +1389,16 @@
       <c r="B20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="20"/>
-      <c r="G20" s="20">
+      <c r="C20" s="12"/>
+      <c r="G20" s="12">
         <v>-5544</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B21" s="29" t="s">
+      <c r="B21" s="21" t="s">
         <v>18</v>
       </c>
       <c r="C21" s="7"/>
@@ -1390,7 +1407,7 @@
       <c r="B22" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F22" s="20">
+      <c r="F22" s="12">
         <v>-3040</v>
       </c>
     </row>
@@ -1398,7 +1415,7 @@
       <c r="B23" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="20"/>
+      <c r="C23" s="12"/>
       <c r="D23" s="3">
         <v>7</v>
       </c>
@@ -1418,10 +1435,10 @@
       <c r="B25" s="3"/>
     </row>
     <row r="26" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="18" t="s">
+      <c r="A26" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B26" s="29" t="s">
+      <c r="B26" s="21" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1443,7 +1460,7 @@
       <c r="D28" s="3">
         <v>4</v>
       </c>
-      <c r="F28" s="20">
+      <c r="F28" s="12">
         <v>2448</v>
       </c>
     </row>
@@ -1451,7 +1468,8 @@
       <c r="B29" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G29" s="20">
+      <c r="F29" s="54"/>
+      <c r="G29" s="12">
         <v>2843</v>
       </c>
     </row>
@@ -1465,19 +1483,19 @@
       <c r="D31" s="3">
         <v>5</v>
       </c>
-      <c r="G31" s="20">
+      <c r="G31" s="12">
         <v>5241</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="18" t="s">
+      <c r="A32" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B32" s="19" t="s">
+      <c r="B32" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="21"/>
-      <c r="G32" s="23">
+      <c r="C32" s="13"/>
+      <c r="G32" s="15">
         <v>1865667</v>
       </c>
     </row>
@@ -1485,8 +1503,8 @@
       <c r="B33" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C33" s="20"/>
-      <c r="G33" s="20">
+      <c r="C33" s="12"/>
+      <c r="G33" s="12">
         <v>1865670</v>
       </c>
     </row>
@@ -1494,8 +1512,8 @@
       <c r="B34" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="20"/>
-      <c r="G34" s="20">
+      <c r="C34" s="12"/>
+      <c r="G34" s="12">
         <v>173134</v>
       </c>
     </row>
@@ -1503,7 +1521,7 @@
       <c r="B35" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G35" s="25">
+      <c r="G35" s="17">
         <v>6925</v>
       </c>
     </row>
@@ -1511,7 +1529,7 @@
       <c r="B36" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G36" s="20">
+      <c r="G36" s="12">
         <v>180059</v>
       </c>
     </row>
@@ -1522,18 +1540,18 @@
       <c r="D37" s="3">
         <v>6</v>
       </c>
-      <c r="G37" s="20">
+      <c r="G37" s="12">
         <v>180059</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="18" t="s">
+      <c r="A38" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B38" s="19" t="s">
+      <c r="B38" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="G38" s="27" t="s">
+      <c r="G38" s="19" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1541,12 +1559,12 @@
       <c r="B39" s="3"/>
     </row>
     <row r="40" spans="1:7" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="15" t="s">
+      <c r="B40" s="8" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="31" t="s">
+      <c r="B41" s="23" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1574,21 +1592,21 @@
       <c r="B46" s="3"/>
     </row>
     <row r="47" spans="1:7" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="15" t="s">
+      <c r="B47" s="8" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="30" t="s">
+      <c r="B48" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="E48" s="22" t="s">
+      <c r="E48" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="F48" s="22" t="s">
+      <c r="F48" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="G48" s="22" t="s">
+      <c r="G48" s="14" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1596,25 +1614,25 @@
       <c r="B49" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E49" s="20">
+      <c r="E49" s="12">
         <v>1940667</v>
       </c>
-      <c r="G49" s="20">
+      <c r="G49" s="12">
         <v>1940667</v>
       </c>
     </row>
     <row r="50" spans="2:7" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="51" spans="2:7" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="30" t="s">
+      <c r="B51" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="E51" s="22" t="s">
+      <c r="E51" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="F51" s="22" t="s">
+      <c r="F51" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="G51" s="22" t="s">
+      <c r="G51" s="14" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1622,10 +1640,10 @@
       <c r="B52" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E52" s="20">
+      <c r="E52" s="12">
         <v>1940667</v>
       </c>
-      <c r="G52" s="20">
+      <c r="G52" s="12">
         <v>1940667</v>
       </c>
     </row>
@@ -1633,10 +1651,10 @@
       <c r="B53" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E53" s="23">
+      <c r="E53" s="15">
         <v>1940667</v>
       </c>
-      <c r="G53" s="23">
+      <c r="G53" s="15">
         <v>1940667</v>
       </c>
     </row>
@@ -1644,23 +1662,23 @@
       <c r="B54" s="3"/>
     </row>
     <row r="55" spans="2:7" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="15" t="s">
+      <c r="B55" s="8" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="56" spans="2:7" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="31" t="s">
+      <c r="B56" s="23" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="57" spans="2:7" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="30" t="s">
+      <c r="B57" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="E57" s="22" t="s">
+      <c r="E57" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="G57" s="22" t="s">
+      <c r="G57" s="14" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1690,7 +1708,7 @@
       <c r="B60" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E60" s="24">
+      <c r="E60" s="16">
         <v>395</v>
       </c>
     </row>
@@ -1698,7 +1716,7 @@
       <c r="B61" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="F61" s="26">
+      <c r="F61" s="18">
         <v>395</v>
       </c>
     </row>
@@ -1706,25 +1724,25 @@
       <c r="B62" s="3"/>
     </row>
     <row r="63" spans="2:7" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="15" t="s">
+      <c r="B63" s="8" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="64" spans="2:7" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="31" t="s">
+      <c r="B64" s="23" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="65" spans="2:5" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="30" t="s">
+      <c r="B65" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="E65" s="22" t="s">
+      <c r="E65" s="14" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="66" spans="2:5" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="32" t="s">
+      <c r="B66" s="24" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1732,7 +1750,7 @@
       <c r="B67" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E67" s="20">
+      <c r="E67" s="12">
         <v>1290</v>
       </c>
     </row>
@@ -1772,7 +1790,7 @@
       <c r="B72" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E72" s="23">
+      <c r="E72" s="15">
         <v>2448</v>
       </c>
     </row>
@@ -1780,7 +1798,7 @@
       <c r="B73" s="3"/>
     </row>
     <row r="74" spans="2:5" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="15" t="s">
+      <c r="B74" s="8" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1789,7 +1807,7 @@
         <v>71</v>
       </c>
       <c r="C75" s="7"/>
-      <c r="E75" s="22" t="s">
+      <c r="E75" s="14" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1797,7 +1815,7 @@
       <c r="B76" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E76" s="20">
+      <c r="E76" s="12">
         <v>2201</v>
       </c>
     </row>
@@ -1805,7 +1823,7 @@
       <c r="B77" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E77" s="20">
+      <c r="E77" s="12">
         <v>3040</v>
       </c>
     </row>
@@ -1813,7 +1831,7 @@
       <c r="B78" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E78" s="23">
+      <c r="E78" s="15">
         <v>5241</v>
       </c>
     </row>
@@ -1821,7 +1839,7 @@
       <c r="B79" s="3"/>
     </row>
     <row r="80" spans="2:5" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B80" s="15" t="s">
+      <c r="B80" s="8" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1831,16 +1849,16 @@
       </c>
     </row>
     <row r="82" spans="1:7" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B82" s="32" t="s">
+      <c r="B82" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="E82" s="22" t="s">
+      <c r="E82" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="F82" s="22" t="s">
+      <c r="F82" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="G82" s="22" t="s">
+      <c r="G82" s="14" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1848,13 +1866,13 @@
       <c r="B83" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E83" s="20">
+      <c r="E83" s="12">
         <v>180059</v>
       </c>
-      <c r="F83" s="20">
+      <c r="F83" s="12">
         <v>180059</v>
       </c>
-      <c r="G83" s="20">
+      <c r="G83" s="12">
         <v>1929871</v>
       </c>
     </row>
@@ -1862,7 +1880,7 @@
       <c r="B84" s="3"/>
     </row>
     <row r="85" spans="1:7" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B85" s="15" t="s">
+      <c r="B85" s="8" t="s">
         <v>82</v>
       </c>
       <c r="C85" s="7"/>
@@ -1877,13 +1895,13 @@
         <v>102</v>
       </c>
       <c r="C87" s="7"/>
-      <c r="E87" s="22" t="s">
+      <c r="E87" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="F87" s="22" t="s">
+      <c r="F87" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="G87" s="22" t="s">
+      <c r="G87" s="14" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1891,7 +1909,7 @@
       <c r="B88" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C88" s="21"/>
+      <c r="C88" s="13"/>
       <c r="E88" s="7" t="s">
         <v>87</v>
       </c>
@@ -1906,16 +1924,16 @@
     <row r="90" spans="1:7" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="91" spans="1:7" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="92" spans="1:7" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="8" t="s">
+      <c r="A92" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="B92" s="8"/>
+      <c r="B92" s="37"/>
     </row>
     <row r="93" spans="1:7" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="G93" s="16" t="s">
+      <c r="G93" s="9" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1956,577 +1974,583 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:38" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="52" t="s">
         <v>103</v>
       </c>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
       <c r="AL1"/>
     </row>
     <row r="2" spans="2:38" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AL2"/>
     </row>
     <row r="3" spans="2:38" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="45" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
-      <c r="K3" s="33"/>
-      <c r="L3" s="33"/>
-      <c r="M3" s="33"/>
-      <c r="N3" s="33"/>
-      <c r="O3" s="33"/>
-      <c r="P3" s="33"/>
-      <c r="Q3" s="33"/>
-      <c r="R3" s="33"/>
-      <c r="S3" s="33"/>
-      <c r="T3" s="33"/>
-      <c r="U3" s="33"/>
-      <c r="V3" s="33"/>
-      <c r="W3" s="33"/>
-      <c r="X3" s="33"/>
-      <c r="Y3" s="33"/>
-      <c r="Z3" s="33"/>
-      <c r="AA3" s="33"/>
-      <c r="AB3" s="33"/>
-      <c r="AC3" s="33"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="25"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25"/>
+      <c r="S3" s="25"/>
+      <c r="T3" s="25"/>
+      <c r="U3" s="25"/>
+      <c r="V3" s="25"/>
+      <c r="W3" s="25"/>
+      <c r="X3" s="25"/>
+      <c r="Y3" s="25"/>
+      <c r="Z3" s="25"/>
+      <c r="AA3" s="25"/>
+      <c r="AB3" s="25"/>
+      <c r="AC3" s="25"/>
     </row>
     <row r="4" spans="2:38" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="36"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="33"/>
-      <c r="M4" s="33"/>
-      <c r="N4" s="33"/>
-      <c r="O4" s="33"/>
-      <c r="P4" s="33"/>
-      <c r="Q4" s="33"/>
-      <c r="R4" s="33"/>
-      <c r="S4" s="33"/>
-      <c r="T4" s="33"/>
-      <c r="U4" s="33"/>
-      <c r="V4" s="33"/>
-      <c r="W4" s="33"/>
-      <c r="X4" s="33"/>
-      <c r="Y4" s="33"/>
-      <c r="Z4" s="33"/>
-      <c r="AA4" s="33"/>
-      <c r="AB4" s="33"/>
-      <c r="AC4" s="33"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
+      <c r="N4" s="25"/>
+      <c r="O4" s="25"/>
+      <c r="P4" s="25"/>
+      <c r="Q4" s="25"/>
+      <c r="R4" s="25"/>
+      <c r="S4" s="25"/>
+      <c r="T4" s="25"/>
+      <c r="U4" s="25"/>
+      <c r="V4" s="25"/>
+      <c r="W4" s="25"/>
+      <c r="X4" s="25"/>
+      <c r="Y4" s="25"/>
+      <c r="Z4" s="25"/>
+      <c r="AA4" s="25"/>
+      <c r="AB4" s="25"/>
+      <c r="AC4" s="25"/>
     </row>
     <row r="5" spans="2:38" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="36"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="33"/>
-      <c r="M5" s="33"/>
-      <c r="N5" s="33"/>
-      <c r="O5" s="33"/>
-      <c r="P5" s="33"/>
-      <c r="Q5" s="33"/>
-      <c r="R5" s="33"/>
-      <c r="S5" s="33"/>
-      <c r="T5" s="33"/>
-      <c r="U5" s="33"/>
-      <c r="V5" s="33"/>
-      <c r="W5" s="33"/>
-      <c r="X5" s="33"/>
-      <c r="Y5" s="33"/>
-      <c r="Z5" s="33"/>
-      <c r="AA5" s="33"/>
-      <c r="AB5" s="33"/>
-      <c r="AC5" s="33"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
+      <c r="M5" s="25"/>
+      <c r="N5" s="25"/>
+      <c r="O5" s="25"/>
+      <c r="P5" s="25"/>
+      <c r="Q5" s="25"/>
+      <c r="R5" s="25"/>
+      <c r="S5" s="25"/>
+      <c r="T5" s="25"/>
+      <c r="U5" s="25"/>
+      <c r="V5" s="25"/>
+      <c r="W5" s="25"/>
+      <c r="X5" s="25"/>
+      <c r="Y5" s="25"/>
+      <c r="Z5" s="25"/>
+      <c r="AA5" s="25"/>
+      <c r="AB5" s="25"/>
+      <c r="AC5" s="25"/>
     </row>
     <row r="6" spans="2:38" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="47" t="s">
+      <c r="B6" s="49" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="48"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="50"/>
-      <c r="L6" s="50"/>
-      <c r="M6" s="50"/>
-      <c r="N6" s="33"/>
-      <c r="O6" s="33"/>
-      <c r="P6" s="33"/>
-      <c r="Q6" s="33"/>
-      <c r="R6" s="33"/>
-      <c r="S6" s="33"/>
-      <c r="T6" s="33"/>
-      <c r="U6" s="33"/>
-      <c r="V6" s="33"/>
-      <c r="W6" s="33"/>
-      <c r="X6" s="33"/>
-      <c r="Y6" s="33"/>
-      <c r="Z6" s="33"/>
-      <c r="AA6" s="33"/>
-      <c r="AB6" s="33"/>
-      <c r="AC6" s="33"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="25"/>
+      <c r="O6" s="25"/>
+      <c r="P6" s="25"/>
+      <c r="Q6" s="25"/>
+      <c r="R6" s="25"/>
+      <c r="S6" s="25"/>
+      <c r="T6" s="25"/>
+      <c r="U6" s="25"/>
+      <c r="V6" s="25"/>
+      <c r="W6" s="25"/>
+      <c r="X6" s="25"/>
+      <c r="Y6" s="25"/>
+      <c r="Z6" s="25"/>
+      <c r="AA6" s="25"/>
+      <c r="AB6" s="25"/>
+      <c r="AC6" s="25"/>
     </row>
     <row r="7" spans="2:38" ht="25.5" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D7" s="33" t="s">
+      <c r="D7" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="E7" s="33" t="s">
+      <c r="E7" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="F7" s="33" t="s">
+      <c r="F7" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="G7" s="33" t="s">
+      <c r="G7" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="H7" s="33" t="s">
+      <c r="H7" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="I7" s="33" t="s">
+      <c r="I7" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="J7" s="33" t="s">
+      <c r="J7" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="K7" s="33" t="s">
+      <c r="K7" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="L7" s="33" t="s">
+      <c r="L7" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="M7" s="33" t="s">
+      <c r="M7" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="N7" s="33"/>
-      <c r="O7" s="33"/>
-      <c r="P7" s="33"/>
-      <c r="Q7" s="33"/>
-      <c r="R7" s="33"/>
-      <c r="S7" s="33"/>
-      <c r="T7" s="33"/>
-      <c r="U7" s="33"/>
-      <c r="V7" s="33"/>
-      <c r="W7" s="33"/>
-      <c r="X7" s="33"/>
-      <c r="Y7" s="33"/>
-      <c r="Z7" s="33"/>
-      <c r="AA7" s="33"/>
-      <c r="AB7" s="33"/>
-      <c r="AC7" s="33"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="25"/>
+      <c r="Q7" s="25"/>
+      <c r="R7" s="25"/>
+      <c r="S7" s="25"/>
+      <c r="T7" s="25"/>
+      <c r="U7" s="25"/>
+      <c r="V7" s="25"/>
+      <c r="W7" s="25"/>
+      <c r="X7" s="25"/>
+      <c r="Y7" s="25"/>
+      <c r="Z7" s="25"/>
+      <c r="AA7" s="25"/>
+      <c r="AB7" s="25"/>
+      <c r="AC7" s="25"/>
     </row>
     <row r="8" spans="2:38" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="B8" s="51"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="50" t="s">
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="31" t="s">
         <v>118</v>
       </c>
-      <c r="E8" s="50" t="s">
+      <c r="E8" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="F8" s="50" t="s">
+      <c r="F8" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="G8" s="50" t="s">
+      <c r="G8" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="H8" s="50" t="s">
+      <c r="H8" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="I8" s="50"/>
-      <c r="J8" s="50" t="s">
+      <c r="I8" s="31"/>
+      <c r="J8" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="K8" s="50" t="s">
+      <c r="K8" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="L8" s="50" t="s">
+      <c r="L8" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="M8" s="50" t="s">
+      <c r="M8" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="N8" s="33"/>
-      <c r="O8" s="33"/>
-      <c r="P8" s="33"/>
-      <c r="Q8" s="33"/>
-      <c r="R8" s="33"/>
-      <c r="S8" s="33"/>
-      <c r="T8" s="33"/>
-      <c r="U8" s="33"/>
-      <c r="V8" s="33"/>
-      <c r="W8" s="33"/>
-      <c r="X8" s="33"/>
-      <c r="Y8" s="33"/>
-      <c r="Z8" s="33"/>
-      <c r="AA8" s="33"/>
-      <c r="AB8" s="33"/>
-      <c r="AC8" s="33"/>
+      <c r="N8" s="25"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="25"/>
+      <c r="Q8" s="25"/>
+      <c r="R8" s="25"/>
+      <c r="S8" s="25"/>
+      <c r="T8" s="25"/>
+      <c r="U8" s="25"/>
+      <c r="V8" s="25"/>
+      <c r="W8" s="25"/>
+      <c r="X8" s="25"/>
+      <c r="Y8" s="25"/>
+      <c r="Z8" s="25"/>
+      <c r="AA8" s="25"/>
+      <c r="AB8" s="25"/>
+      <c r="AC8" s="25"/>
     </row>
     <row r="9" spans="2:38" ht="51" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D9" s="33"/>
-      <c r="E9" s="42">
+      <c r="D9" s="25"/>
+      <c r="E9" s="26">
         <v>45756</v>
       </c>
-      <c r="F9" s="33">
+      <c r="F9" s="25">
         <v>745</v>
       </c>
-      <c r="G9" s="33"/>
-      <c r="H9" s="43">
+      <c r="G9" s="25"/>
+      <c r="H9" s="27">
         <v>1675</v>
       </c>
-      <c r="I9" s="33"/>
-      <c r="J9" s="43">
+      <c r="I9" s="25"/>
+      <c r="J9" s="27">
         <v>1675</v>
       </c>
-      <c r="K9" s="33"/>
-      <c r="L9" s="33">
+      <c r="K9" s="25"/>
+      <c r="L9" s="25">
         <v>-930</v>
       </c>
-      <c r="M9" s="33"/>
-      <c r="N9" s="33"/>
-      <c r="O9" s="33"/>
-      <c r="P9" s="33"/>
-      <c r="Q9" s="33"/>
-      <c r="R9" s="33"/>
-      <c r="S9" s="33"/>
-      <c r="T9" s="33"/>
-      <c r="U9" s="33"/>
-      <c r="V9" s="33"/>
-      <c r="W9" s="33"/>
-      <c r="X9" s="33"/>
-      <c r="Y9" s="33"/>
-      <c r="Z9" s="33"/>
-      <c r="AA9" s="33"/>
-      <c r="AB9" s="33"/>
-      <c r="AC9" s="33"/>
+      <c r="M9" s="25"/>
+      <c r="N9" s="25"/>
+      <c r="O9" s="25"/>
+      <c r="P9" s="25"/>
+      <c r="Q9" s="25"/>
+      <c r="R9" s="25"/>
+      <c r="S9" s="25"/>
+      <c r="T9" s="25"/>
+      <c r="U9" s="25"/>
+      <c r="V9" s="25"/>
+      <c r="W9" s="25"/>
+      <c r="X9" s="25"/>
+      <c r="Y9" s="25"/>
+      <c r="Z9" s="25"/>
+      <c r="AA9" s="25"/>
+      <c r="AB9" s="25"/>
+      <c r="AC9" s="25"/>
     </row>
     <row r="10" spans="2:38" ht="51" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D10" s="33"/>
-      <c r="E10" s="42">
+      <c r="D10" s="25"/>
+      <c r="E10" s="26">
         <v>45756</v>
       </c>
-      <c r="F10" s="43">
+      <c r="F10" s="27">
         <v>1490</v>
       </c>
-      <c r="G10" s="33"/>
-      <c r="H10" s="43">
+      <c r="G10" s="25"/>
+      <c r="H10" s="27">
         <v>3600</v>
       </c>
-      <c r="I10" s="33"/>
-      <c r="J10" s="43">
+      <c r="I10" s="25"/>
+      <c r="J10" s="27">
         <v>3600</v>
       </c>
-      <c r="K10" s="33"/>
-      <c r="L10" s="43">
+      <c r="K10" s="25"/>
+      <c r="L10" s="27">
         <v>-2110</v>
       </c>
-      <c r="M10" s="33"/>
-      <c r="N10" s="33"/>
-      <c r="O10" s="33"/>
-      <c r="P10" s="33"/>
-      <c r="Q10" s="33"/>
-      <c r="R10" s="33"/>
-      <c r="S10" s="33"/>
-      <c r="T10" s="33"/>
-      <c r="U10" s="33"/>
-      <c r="V10" s="33"/>
-      <c r="W10" s="33"/>
-      <c r="X10" s="33"/>
-      <c r="Y10" s="33"/>
-      <c r="Z10" s="33"/>
-      <c r="AA10" s="33"/>
-      <c r="AB10" s="33"/>
-      <c r="AC10" s="33"/>
+      <c r="M10" s="25"/>
+      <c r="N10" s="25"/>
+      <c r="O10" s="25"/>
+      <c r="P10" s="25"/>
+      <c r="Q10" s="25"/>
+      <c r="R10" s="25"/>
+      <c r="S10" s="25"/>
+      <c r="T10" s="25"/>
+      <c r="U10" s="25"/>
+      <c r="V10" s="25"/>
+      <c r="W10" s="25"/>
+      <c r="X10" s="25"/>
+      <c r="Y10" s="25"/>
+      <c r="Z10" s="25"/>
+      <c r="AA10" s="25"/>
+      <c r="AB10" s="25"/>
+      <c r="AC10" s="25"/>
     </row>
     <row r="11" spans="2:38" ht="38.25" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D11" s="33"/>
-      <c r="E11" s="42">
+      <c r="D11" s="25"/>
+      <c r="E11" s="26">
         <v>45912</v>
       </c>
-      <c r="F11" s="44">
+      <c r="F11" s="28">
         <v>3124.5</v>
       </c>
-      <c r="G11" s="33"/>
-      <c r="H11" s="43">
+      <c r="G11" s="25"/>
+      <c r="H11" s="27">
         <v>2829</v>
       </c>
-      <c r="I11" s="33"/>
-      <c r="J11" s="43">
+      <c r="I11" s="25"/>
+      <c r="J11" s="27">
         <v>2829</v>
       </c>
-      <c r="K11" s="33">
+      <c r="K11" s="25">
         <v>295.5</v>
       </c>
-      <c r="L11" s="45" t="s">
+      <c r="L11" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="M11" s="33"/>
-      <c r="N11" s="33"/>
-      <c r="O11" s="33"/>
-      <c r="P11" s="33"/>
-      <c r="Q11" s="33"/>
-      <c r="R11" s="33"/>
-      <c r="S11" s="33"/>
-      <c r="T11" s="33"/>
-      <c r="U11" s="33"/>
-      <c r="V11" s="33"/>
-      <c r="W11" s="33"/>
-      <c r="X11" s="33"/>
-      <c r="Y11" s="33"/>
-      <c r="Z11" s="33"/>
-      <c r="AA11" s="33"/>
-      <c r="AB11" s="33"/>
-      <c r="AC11" s="33"/>
+      <c r="M11" s="25"/>
+      <c r="N11" s="25"/>
+      <c r="O11" s="25"/>
+      <c r="P11" s="25"/>
+      <c r="Q11" s="25"/>
+      <c r="R11" s="25"/>
+      <c r="S11" s="25"/>
+      <c r="T11" s="25"/>
+      <c r="U11" s="25"/>
+      <c r="V11" s="25"/>
+      <c r="W11" s="25"/>
+      <c r="X11" s="25"/>
+      <c r="Y11" s="25"/>
+      <c r="Z11" s="25"/>
+      <c r="AA11" s="25"/>
+      <c r="AB11" s="25"/>
+      <c r="AC11" s="25"/>
     </row>
     <row r="12" spans="2:38" ht="38.25" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D12" s="33"/>
-      <c r="E12" s="42">
+      <c r="D12" s="25"/>
+      <c r="E12" s="26">
         <v>45912</v>
       </c>
-      <c r="F12" s="43">
+      <c r="F12" s="27">
         <v>2083</v>
       </c>
-      <c r="G12" s="33"/>
-      <c r="H12" s="43">
+      <c r="G12" s="25"/>
+      <c r="H12" s="27">
         <v>1860</v>
       </c>
-      <c r="I12" s="33"/>
-      <c r="J12" s="43">
+      <c r="I12" s="25"/>
+      <c r="J12" s="27">
         <v>1860</v>
       </c>
-      <c r="K12" s="33">
+      <c r="K12" s="25">
         <v>223</v>
       </c>
-      <c r="L12" s="45" t="s">
+      <c r="L12" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="M12" s="33"/>
-      <c r="N12" s="33"/>
-      <c r="O12" s="33"/>
-      <c r="P12" s="33"/>
-      <c r="Q12" s="33"/>
-      <c r="R12" s="33"/>
-      <c r="S12" s="33"/>
-      <c r="T12" s="33"/>
-      <c r="U12" s="33"/>
-      <c r="V12" s="33"/>
-      <c r="W12" s="33"/>
-      <c r="X12" s="33"/>
-      <c r="Y12" s="33"/>
-      <c r="Z12" s="33"/>
-      <c r="AA12" s="33"/>
-      <c r="AB12" s="33"/>
-      <c r="AC12" s="33"/>
+      <c r="M12" s="25"/>
+      <c r="N12" s="25"/>
+      <c r="O12" s="25"/>
+      <c r="P12" s="25"/>
+      <c r="Q12" s="25"/>
+      <c r="R12" s="25"/>
+      <c r="S12" s="25"/>
+      <c r="T12" s="25"/>
+      <c r="U12" s="25"/>
+      <c r="V12" s="25"/>
+      <c r="W12" s="25"/>
+      <c r="X12" s="25"/>
+      <c r="Y12" s="25"/>
+      <c r="Z12" s="25"/>
+      <c r="AA12" s="25"/>
+      <c r="AB12" s="25"/>
+      <c r="AC12" s="25"/>
     </row>
     <row r="13" spans="2:38" ht="38.25" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D13" s="33"/>
-      <c r="E13" s="42">
+      <c r="D13" s="25"/>
+      <c r="E13" s="26">
         <v>45912</v>
       </c>
-      <c r="F13" s="44">
+      <c r="F13" s="28">
         <v>1041.5</v>
       </c>
-      <c r="G13" s="33"/>
-      <c r="H13" s="43">
+      <c r="G13" s="25"/>
+      <c r="H13" s="27">
         <v>1060</v>
       </c>
-      <c r="I13" s="33"/>
-      <c r="J13" s="43">
+      <c r="I13" s="25"/>
+      <c r="J13" s="27">
         <v>1060</v>
       </c>
-      <c r="K13" s="33">
+      <c r="K13" s="25">
         <v>-18.5</v>
       </c>
-      <c r="L13" s="45" t="s">
+      <c r="L13" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="M13" s="33"/>
-      <c r="N13" s="33"/>
-      <c r="O13" s="33"/>
-      <c r="P13" s="33"/>
-      <c r="Q13" s="33"/>
-      <c r="R13" s="33"/>
-      <c r="S13" s="33"/>
-      <c r="T13" s="33"/>
-      <c r="U13" s="33"/>
-      <c r="V13" s="33"/>
-      <c r="W13" s="33"/>
-      <c r="X13" s="33"/>
-      <c r="Y13" s="33"/>
-      <c r="Z13" s="33"/>
-      <c r="AA13" s="33"/>
-      <c r="AB13" s="33"/>
-      <c r="AC13" s="33"/>
+      <c r="M13" s="25"/>
+      <c r="N13" s="25"/>
+      <c r="O13" s="25"/>
+      <c r="P13" s="25"/>
+      <c r="Q13" s="25"/>
+      <c r="R13" s="25"/>
+      <c r="S13" s="25"/>
+      <c r="T13" s="25"/>
+      <c r="U13" s="25"/>
+      <c r="V13" s="25"/>
+      <c r="W13" s="25"/>
+      <c r="X13" s="25"/>
+      <c r="Y13" s="25"/>
+      <c r="Z13" s="25"/>
+      <c r="AA13" s="25"/>
+      <c r="AB13" s="25"/>
+      <c r="AC13" s="25"/>
     </row>
     <row r="14" spans="2:38" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="46" t="s">
+      <c r="B14" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="52"/>
-      <c r="E14" s="52"/>
-      <c r="F14" s="53">
+      <c r="C14" s="30"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="34">
         <v>8484</v>
       </c>
-      <c r="G14" s="52"/>
-      <c r="H14" s="53">
+      <c r="G14" s="33"/>
+      <c r="H14" s="34">
         <v>11024</v>
       </c>
-      <c r="I14" s="52"/>
-      <c r="J14" s="53">
+      <c r="I14" s="33"/>
+      <c r="J14" s="34">
         <v>11024</v>
       </c>
-      <c r="K14" s="52">
+      <c r="K14" s="33">
         <v>500</v>
       </c>
-      <c r="L14" s="53">
+      <c r="L14" s="34">
         <v>-3040</v>
       </c>
-      <c r="M14" s="52"/>
-      <c r="N14" s="33"/>
-      <c r="O14" s="33"/>
-      <c r="P14" s="33"/>
-      <c r="Q14" s="33"/>
-      <c r="R14" s="33"/>
-      <c r="S14" s="33"/>
-      <c r="T14" s="33"/>
-      <c r="U14" s="33"/>
-      <c r="V14" s="33"/>
-      <c r="W14" s="33"/>
-      <c r="X14" s="33"/>
-      <c r="Y14" s="33"/>
-      <c r="Z14" s="33"/>
-      <c r="AA14" s="33"/>
-      <c r="AB14" s="33"/>
-      <c r="AC14" s="33"/>
+      <c r="M14" s="33"/>
+      <c r="N14" s="25"/>
+      <c r="O14" s="25"/>
+      <c r="P14" s="25"/>
+      <c r="Q14" s="25"/>
+      <c r="R14" s="25"/>
+      <c r="S14" s="25"/>
+      <c r="T14" s="25"/>
+      <c r="U14" s="25"/>
+      <c r="V14" s="25"/>
+      <c r="W14" s="25"/>
+      <c r="X14" s="25"/>
+      <c r="Y14" s="25"/>
+      <c r="Z14" s="25"/>
+      <c r="AA14" s="25"/>
+      <c r="AB14" s="25"/>
+      <c r="AC14" s="25"/>
     </row>
     <row r="15" spans="2:38" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="33"/>
-      <c r="K15" s="33"/>
-      <c r="L15" s="33"/>
-      <c r="M15" s="33"/>
-      <c r="N15" s="33"/>
-      <c r="O15" s="33"/>
-      <c r="P15" s="33"/>
-      <c r="Q15" s="33"/>
-      <c r="R15" s="33"/>
-      <c r="S15" s="33"/>
-      <c r="T15" s="33"/>
-      <c r="U15" s="33"/>
-      <c r="V15" s="33"/>
-      <c r="W15" s="33"/>
-      <c r="X15" s="33"/>
-      <c r="Y15" s="33"/>
-      <c r="Z15" s="33"/>
-      <c r="AA15" s="33"/>
-      <c r="AB15" s="33"/>
-      <c r="AC15" s="33"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="25"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="25"/>
+      <c r="M15" s="25"/>
+      <c r="N15" s="25"/>
+      <c r="O15" s="25"/>
+      <c r="P15" s="25"/>
+      <c r="Q15" s="25"/>
+      <c r="R15" s="25"/>
+      <c r="S15" s="25"/>
+      <c r="T15" s="25"/>
+      <c r="U15" s="25"/>
+      <c r="V15" s="25"/>
+      <c r="W15" s="25"/>
+      <c r="X15" s="25"/>
+      <c r="Y15" s="25"/>
+      <c r="Z15" s="25"/>
+      <c r="AA15" s="25"/>
+      <c r="AB15" s="25"/>
+      <c r="AC15" s="25"/>
     </row>
     <row r="16" spans="2:38" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="33"/>
-      <c r="K16" s="33"/>
-      <c r="L16" s="33"/>
-      <c r="M16" s="33"/>
-      <c r="N16" s="33"/>
-      <c r="O16" s="33"/>
-      <c r="P16" s="33"/>
-      <c r="Q16" s="33"/>
-      <c r="R16" s="33"/>
-      <c r="S16" s="33"/>
-      <c r="T16" s="33"/>
-      <c r="U16" s="33"/>
-      <c r="V16" s="33"/>
-      <c r="W16" s="33"/>
-      <c r="X16" s="33"/>
-      <c r="Y16" s="33"/>
-      <c r="Z16" s="33"/>
-      <c r="AA16" s="33"/>
-      <c r="AB16" s="33"/>
-      <c r="AC16" s="33"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="25"/>
+      <c r="O16" s="25"/>
+      <c r="P16" s="25"/>
+      <c r="Q16" s="25"/>
+      <c r="R16" s="25"/>
+      <c r="S16" s="25"/>
+      <c r="T16" s="25"/>
+      <c r="U16" s="25"/>
+      <c r="V16" s="25"/>
+      <c r="W16" s="25"/>
+      <c r="X16" s="25"/>
+      <c r="Y16" s="25"/>
+      <c r="Z16" s="25"/>
+      <c r="AA16" s="25"/>
+      <c r="AB16" s="25"/>
+      <c r="AC16" s="25"/>
     </row>
     <row r="17" spans="8:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="18" spans="8:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="19" spans="8:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="20" spans="8:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="21" spans="8:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H21" s="41" t="s">
+      <c r="H21" s="43" t="s">
         <v>92</v>
       </c>
-      <c r="I21" s="34"/>
-      <c r="J21" s="34"/>
-      <c r="K21" s="34"/>
-      <c r="L21" s="34"/>
+      <c r="I21" s="44"/>
+      <c r="J21" s="44"/>
+      <c r="K21" s="44"/>
+      <c r="L21" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B1:F1"/>
     <mergeCell ref="H21:L21"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B1:F1"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.35" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{1b5d643d-5daa-4182-b4ec-05c4e602cf56}" enabled="1" method="Privileged" siteId="{50f40674-931c-4d09-ae8a-bb8fde36b912}" removed="0"/>
+</clbl:labelList>
 </file>